--- a/docs/Reports & Plans/LSO-Knights-List-and-Analysis.xlsx
+++ b/docs/Reports & Plans/LSO-Knights-List-and-Analysis.xlsx
@@ -651,17 +651,17 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Volcano lance, plasma decimator, 2x twin meltagun, 2x shieldbreaker, twin siegebreaker, feet</t>
+          <t>Volcano lance (D3 shots S18 AP-5 D6+8), plasma decimator (D6+3 shots), 2x twin meltagun, 2x shieldbreaker, twin siegebreaker, feet</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>435 ea</t>
+          <t>400 ea</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>The shooting core. 2x Volcano one-shots no-invuln anchors + snipes characters @60"; plasma anti-elite; +1 hit vs terrain (Dominus).</t>
+          <t>The shooting core. 2x Volcano (D3 shots ea, ~23 dmg) one-shots no-invuln anchors + snipes characters; plasma decimator anti-elite volume; +1 hit vs terrain (Dominus).</t>
         </is>
       </c>
     </row>
@@ -676,17 +676,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Rapid-fire battle cannon, Avenger gatling cannon, heavy flamer, thermal cannon, 2x stubber, feet</t>
+          <t>Rapid-fire battle cannon (D6+3 S10), Avenger gatling (A18 S6 AP-2 D2), heavy flamer, thermal cannon (2D3 S12 AP-4 Melta6), stubber, feet</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>~435</t>
+          <t>395</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Anti-infantry SUBTRACTION: RFBC (D6+3) + Avenger A18 strip soft OC; thermal for anti-tank/Speeders.</t>
+          <t>Anti-infantry SUBTRACTION: RFBC + Avenger A18 strip soft OC; thermal for anti-tank/Speeders.</t>
         </is>
       </c>
     </row>
@@ -701,17 +701,17 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Cerastus shock lance (strike S20 AP-3 D8 [Lance] / sweep A10 S10 AP-2 D3), ranged shock lance</t>
+          <t>Shock lance — strike 5A S20 AP-3 D8 [Lance] / sweep 10A S10 AP-2 D3; ranged shock lance 12" 6A [Assault, Sus2]</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>~415</t>
+          <t>415</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>The one blade: 4++ FULL invuln, M14. Counter-charge melee threats + assassinate buff-characters + free Crushing Impact MW on the charge.</t>
+          <t>The one blade: 4++ FULL invuln vs ALL, M14 W28. Counter-charge + assassinate buff-characters + Shock-Charge free Tank Shock on the charge.</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1781,30 +1781,190 @@
     <row r="24" ht="60" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
+          <t>T'au Empire</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Retaliation Cadre (deep-strike fusion/rail alpha) — TOP-5 OBSERVED</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>UNFAVOURABLE</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>The DOMINANT T'au build in the sample (5/75). Deep-strike alpha: 4-5 Commanders + Crisis Sunforge (fusion S9 AP-4 D6), Broadside heavy rail (S12+ AP-4 Dev), Twin Lance, 2x Riptide ion accelerator, markerlight support. A markerlit 9" Sunforge/Crisis drop dumps ~25-35 into ONE Knight (fusion D6 + rail Dev bypass the ion shield). Fire-and-Fade neuters melee.</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>• NAVIGATOR DOME IS LOAD-BEARING: the 12" anti-Deep-Strike bubble denies the Sunforge/Crisis 9" drop — the single biggest swing in the matchup. Deploy it central.
+• Kill the Broadsides + Riptides at range (Volcano/plasma) before markerlights stack; delete Pathfinders (the mark engine) with the Avenger.
+• Rotate the most-lit Knight each turn; never present a clean un-Rotated focus target; LoS-block the alpha turn.
+• Out-OC on the ground (T'au OC is modest) IF you survive the alpha — steal the primary while their suits reposition.</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Broadsides / Riptides (rail+ion) -&gt; Sunforge fusion suits -&gt; markerlight Pathfinders -&gt; Commanders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Chaos Daemons</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Blood Legion — Bloodcrusher cavalry + Bloodthirster</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>COIN-FLIP</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Fast MELEE alpha: 3x Skullmaster + Bloodcrusher Juggernaut cav (T6 W4, charge bonuses) + Bloodthirster (T10 W18 FLY, great axe S16 AP-3 Dev) + Rendmasters. Daemonic 5++ everywhere; charges into the no-melee-invuln Questoris. (Nurgle variant = Plaguebearer grind, slower, out-hold problem not a kill problem.)</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>• Shoot the Bloodcrushers (T6 W4, no armour help — gatling/plasma/RFBC) OFF before they charge; each un-charged Juggernaut pack is ~0 threat.
+• Screen the Bloodthirster's lane; Lancer DUELS it (4++ trades favourably, S20 one-rounds a wounded 'Thirster) rather than eating its charge on a Castellan.
+• Rotate the exposed Knight vs the (modest) ranged; out-OC the cav once thinned.
+• vs Nurgle grind: ignore the tarpit, out-shoot Plaguebearers off objectives, win on tempo.</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Bloodthirster (or screen) -&gt; Bloodcrushers pre-charge -&gt; Skullmasters / Rendmasters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Astra Militarum</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Steel Hammer superheavies / Grizzled artillery — OBSERVED</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>COIN-FLIP</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>A SHOOTING brawl in my lane: Baneblade/Banesword/Stormsword (CHARACTER via Steel Hammer) + lascannon sponsons, or Shadowsword (Volcano cannon S16 AP-4 D6+6 — one-shots a Knight) + 3 artillery + Leman Russ. High-S anti-Knight, but the superheavies are KILLABLE (T12-14 W22-24, no invuln) and SLOW.</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>• Win the gun duel: 2x Volcano (S18) out-ranges/out-damages their superheavies — delete the Shadowsword (the one thing that one-shots you) FIRST, then the lascannon platforms.
+• Rotate vs the alpha; hull-down T1; their artillery is indirect (worse into a moving Knight in cover).
+• Out-manoeuvre the M9-10 tanks + out-OC (Guard infantry is chaff you gun down); race the mission.
+• This is the matchup the 2-Castellan build is BUILT for — a straight firepower race.</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Shadowsword (Volcano cannon) -&gt; lascannon superheavies -&gt; artillery -&gt; Leontus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Space Marines (Iron Hands)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Hammer of Avernii — Assault Terminator hammer brick — OBSERVED</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>COIN-FLIP</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>10-model Assault Terminator thunder-hammer brick (S8 AP-2 D2, ~12-16 into a no-invuln Questoris on the charge) delivered by deep-strike + Celerity advance-charge, Feirros durability, Ballistus/Repulsor lascannon backfield. The brick is the only real Knight-killer; the rest is chaff/scorers.</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>• Screen the deep-strike (Navigator dome) + shoot the hammer brick BEFORE it lands (Avenger/RFBC into 2W-2+ Terminators — volume forces the 4++).
+• Lancer counter-charges the landed brick (4++ survives hammers a Castellan can't); never feed a Questoris into its charge.
+• Delete the Repulsor/Ballistus (lascannon) + Sternguard with the big guns; out-OC the ~30 bodies.
+• Win on the mission — the brick can't be everywhere; contest what it isn't on with OC10.</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Repulsor/Ballistus (lascannon) -&gt; hammer brick as it lands -&gt; Sternguard -&gt; Scouts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
           <t>Imperial Fists</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>'Great Value' — Emperor's Shield + Librarius Conclave (the LSO target)</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>COIN-FLIP</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>Unsaveable Sternguard Dev (full wound-reroll vs Oath) + sticky OC10 Intercessors + un-shockable OC22 Lysander Terminator brick + Armour of Contempt + a ~30-34 Oath-convergence alpha. Sisters 98-31 lesson: durable + sticky + volume.</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>• Navigator dome (12" anti-Deep-Strike) blunts his Teleport-Homer / Land-Speeder deep-strike alpha.
 • BREAK the Oath convergence: Volcano/thermal the Land Speeders (deep-strike enablers) + the Sternguard FIRST; firepower-as-denial strips his soft OC.
@@ -1812,7 +1972,7 @@
 • Start from EXPECTATION OF A LOSS; steal via mobility secondaries. Honest coin-flip (~55-56 vs 62 in the hardened sim).</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>Land Speeders (enablers) -&gt; Sternguard (unsaveable Dev) -&gt; break the brick's character support.</t>
         </is>
@@ -1878,19 +2038,19 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Valourstrike stratagem, once per phase -&gt; upgrade ONE Knight to 4++ vs shooting each turn. Only one protected per shooting phase.</t>
+          <t>The durability lever: upgrade ONE Knight to 4++ vs shooting each turn. [VERIFY exact Valourstrike stratagem name/wording vs the LIVE faction pack — the 11E datasheet Ion Shield is the printed '5+* vs ranged only'; confirm the detachment grants the per-turn 4++.]</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="20" t="inlineStr">
         <is>
-          <t>Questoris melee</t>
+          <t>Questoris/Dominus melee</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>NO melee invuln — bare 3+ armour in the fight phase. Melee is the universal Knight weakness.</t>
+          <t>NO melee invuln (verified — printed 5+* is 'vs ranged attacks only') — bare 3+ armour in the fight phase. Melee is the universal Knight weakness (only the Sanctuary enhancement adds a melee 5++).</t>
         </is>
       </c>
     </row>
@@ -1902,7 +2062,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>4++ FULL invuln (melee AND ranged), M14. Strike S20 AP-3 D8 [Lance]; free Crushing Impact on charge (D6=T11, each 5+ = 1 MW, bypasses invuln). The universal counter-charge + character-assassin.</t>
+          <t>VERIFIED 415pts, M14 T11 W28, 4++ invuln vs ALL attacks (no asterisk). Shock lance STRIKE 5A WS2+ S20 AP-3 D8 [Lance] (wounds anything &lt;=T12 on 2s) / SWEEP 10A S10 AP-2 D3. Shock Charge = free Tank Shock (0CP, repeatable) on the charge = bonus MW. The universal counter-charge + character-assassin.</t>
         </is>
       </c>
     </row>
@@ -1914,7 +2074,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>S18 AP-5 D6+8 — one-shots no-invuln anchors (Hammerheads, Land Raiders, Kataphrons, Monoliths, no-invuln Norns). Wasted (overkill) into low-W chaff.</t>
+          <t>VERIFIED 72" D3 SHOTS (avg 2), S18 AP-5 D6+8 [Blast] — ~23 dmg/turn; one-shots no-invuln anchors (Hammerheads T10, Land Raiders T12, Kataphrons, Shadowsword, no-invuln Norns/Emissaries). Overkill into low-W chaff. The Castellan is 400pts (BSData; app may price 425 — verify vs live MFM).</t>
         </is>
       </c>
     </row>

--- a/docs/Reports & Plans/LSO-Knights-List-and-Analysis.xlsx
+++ b/docs/Reports & Plans/LSO-Knights-List-and-Analysis.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>As written ~1825-1915 / 2000 with NO enhancements = the one concrete error. Add the 3 enhancements above to reach 2000 (Rotate is free). VERIFY exact points vs LIVE MFM before submitting — BSData prices Castellan 400, the app may be 425.</t>
+          <t>VERIFIED 1,995 / 2000: 2x Castellan 400 + Cerastus Lancer 415 + Crusader 395 + 2x Armiger Helverin 140 + Navigator 75 = 1,965, + Blessed Plate 30 = 1,995 (5 spare). Points from BSData = current MFM (Castellan 400 confirmed, not 425). NO Lancer's Sigil (rejected). The 2nd Armiger is the points-efficient fill — a single Armiger wastes ~95 pts the enhancement allowance can't absorb.</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -731,12 +731,12 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>140 ea</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Backfield 48" autocannons + cheap OC6 body / screen.</t>
+          <t>TWO backfield 48" autocannon platforms + OC6 screens — the points-efficient fill (a single Armiger wastes ~95 pts) + extra OC for the melee-heavy meta.</t>
         </is>
       </c>
     </row>
@@ -799,22 +799,22 @@
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Bearer of the Lancer's Sigil</t>
+          <t>Blessed Plate  [TAKEN]</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Cerastus Knight Lancer</t>
+          <t>a Knight Castellan</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Re-roll the Lancer's charge — with only ONE decapitation blade, guaranteeing its decisive charge is the highest-value 25 pts in the list.</t>
+          <t>Castellan -&gt; T13: pushes S12-13 anti-tank (rail / ferrumite / lascannon / Caladius / thermal) from wounding on 4+ to 5+ — survivability for the key Volcano platform. The 2-Armiger build fits ~one enhancement; this is it.</t>
         </is>
       </c>
       <c r="E17" s="9" t="n"/>
@@ -822,22 +822,22 @@
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Blessed Plate</t>
+          <t>Bearer of the Judicant's Helm  [bench]</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Knight Castellan #1</t>
+          <t>a Knight Castellan</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Castellan -&gt; T13: the Volcano platform survives the incoming longer.</t>
+          <t>[Ignores Cover] on a Castellan — stacks with Dominus +1-hit-in-terrain. Offensive alternative to Blessed Plate.</t>
         </is>
       </c>
       <c r="E18" s="9" t="n"/>
@@ -845,22 +845,22 @@
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Bearer of the Judicant's Helm</t>
+          <t>Sanctuary  [bench]</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Knight Castellan #2</t>
+          <t>a Knight Castellan</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>[Ignores Cover] on a Castellan — stacks with Dominus +1-hit-in-terrain; beats intervening-terrain cover.</t>
+          <t>5++ invuln vs MELEE on one Castellan — patches the no-melee-invuln weakness (newly relevant: 11E has NO Rotate Ion Shields and Questoris have no melee save). Consider vs a melee-heavy field.</t>
         </is>
       </c>
       <c r="E19" s="9" t="n"/>
@@ -2173,7 +2173,7 @@
     <row r="2" ht="150" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Realistic 300+ GT expectation (re-verified): a positive-but-underdog record, roughly 3-3 to 4-2 over 5-6 rounds (~55-65% game win rate, pairing-skewed). Bank the broad early/mid field (the favourable + winnable coin-flips); slide toward losses as the top cut concentrates the filth (Necrons/T'au/Ravenwing/AdMech/SW). Correct Knight goal: strong positive + steal a couple you shouldn't win — NOT winning the event. The 2-Castellan shooting core IMPROVES this over 2-Lancer (more removal-race firepower for exactly the hard matchups). List blind spots (priority order): (1) ~85-175 pts unspent + ZERO enhancements = fix to 2000 first; (2) only ONE 4++ Lancer into a melee-heavy field — accepted price of shooting-dominance; mitigate by killing deliverers pre-charge + Lancer's-Sigil charge re-roll, NOT a 2nd blade; (3) screening deep-strike alphas (BA/SW/Votann/GSC) with only ~5 combat models — the Navigator dome is load-bearing; (4) anti-horde is moderate (accept Green Tide); (5) out-OC'd by most of the field -&gt; lock PURGE THE FOE (kill-weighted) over Priority Assets.</t>
+          <t>Realistic 300+ GT expectation (re-verified): a positive-but-underdog record, roughly 3-3 to 4-2 over 5-6 rounds (~55-65% game win rate, pairing-skewed). Bank the broad early/mid field (the favourable + winnable coin-flips); slide toward losses as the top cut concentrates the filth (Necrons/T'au/Ravenwing/AdMech/SW). Correct Knight goal: strong positive + steal a couple you shouldn't win — NOT winning the event. The 2-Castellan shooting core IMPROVES this over 2-Lancer (more removal-race firepower for exactly the hard matchups). List blind spots (priority order): (1) [RESOLVED] now costed to 1,995/2000 (2nd Armiger + Blessed Plate); (2) only ONE 4++ Lancer into a melee-heavy field — accepted price of shooting-dominance; mitigate by killing deliverers pre-charge, NOT a 2nd blade; (3) screening deep-strike alphas (BA/SW/Votann/GSC) with only ~5 combat models — the Navigator dome is load-bearing; (4) anti-horde is moderate (accept Green Tide); (5) out-OC'd by most of the field -&gt; lock PURGE THE FOE (kill-weighted) over Priority Assets.</t>
         </is>
       </c>
     </row>

--- a/docs/Reports & Plans/LSO-Knights-List-and-Analysis.xlsx
+++ b/docs/Reports & Plans/LSO-Knights-List-and-Analysis.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -597,7 +597,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>VERIFIED 1,995 / 2000: 2x Castellan 400 + Cerastus Lancer 415 + Crusader 395 + 2x Armiger Helverin 140 + Navigator 75 = 1,965, + Blessed Plate 30 = 1,995 (5 spare). Points from BSData = current MFM (Castellan 400 confirmed, not 425). NO Lancer's Sigil (rejected). The 2nd Armiger is the points-efficient fill — a single Armiger wastes ~95 pts the enhancement allowance can't absorb.</t>
+          <t>1,970 / 2000 (30 spare) — MFM points: Castellan 425 + 450 (escalating) + Crusader 410 (395 +15 RFBC) + Cerastus Lancer 415 + Armiger Helverin 140 + Navigator 75 = 1,915, + Archeotech Autoloaders 25 + Blessed Plate 30 = 1,970. ONE Armiger (the correct build — the earlier '2 Armiger' was an error from stale BSData points). NO Lancer's Sigil. All points MFM-verified (1,970/2000 from data/mfm/imperial-knights.json).</t>
         </is>
       </c>
     </row>
@@ -656,12 +656,12 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>400 ea</t>
+          <t>425 + 450</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>The shooting core. 2x Volcano (D3 shots ea, ~23 dmg) one-shots no-invuln anchors + snipes characters; plasma decimator anti-elite volume; +1 hit vs terrain (Dominus).</t>
+          <t>The shooting core (escalating: 1st 425, 2nd 450). 2x Volcano (D3 shots ea, ~23 dmg) one-shots no-invuln anchors + snipes; plasma decimator anti-elite; +1 hit vs terrain (Dominus). #1 bears Archeotech Autoloaders (re-roll the shot count on the D3/D6+3 guns).</t>
         </is>
       </c>
     </row>
@@ -676,17 +676,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Rapid-fire battle cannon (D6+3 S10), Avenger gatling (A18 S6 AP-2 D2), heavy flamer, thermal cannon (2D3 S12 AP-4 Melta6), stubber, feet</t>
+          <t>Rapid-fire battle cannon (D6+3 S10, +15pts), Avenger gatling (A18 S6 AP-2 D2), heavy flamer, thermal cannon (2D3 S12 AP-4 Melta6), stubber, feet</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>410</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Anti-infantry SUBTRACTION: RFBC + Avenger A18 strip soft OC; thermal for anti-tank/Speeders.</t>
+          <t>395 base + 15 for the RFBC. Anti-infantry SUBTRACTION: RFBC + Avenger A18 strip soft OC; thermal for anti-tank/Speeders.</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -731,12 +731,12 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>140 ea</t>
+          <t>140</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>TWO backfield 48" autocannon platforms + OC6 screens — the points-efficient fill (a single Armiger wastes ~95 pts) + extra OC for the melee-heavy meta.</t>
+          <t>Backfield 48" autocannon platform + OC6 screen.</t>
         </is>
       </c>
     </row>
@@ -756,12 +756,12 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>~75</t>
+          <t>75</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>12" anti-Deep-Strike dome (vs BA/SW/GSC/deep-strike alphas) + Hidden home-holder. Allies take no enhancement.</t>
+          <t>12" anti-Deep-Strike dome (vs BA/SW/GSC/deep-strike alphas) + Hidden home-holder. Allies take no enhancement. (75 confirmed from Scott Ketcham's Tacoma roster.)</t>
         </is>
       </c>
     </row>
@@ -799,22 +799,22 @@
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Blessed Plate  [TAKEN]</t>
+          <t>Archeotech Autoloaders  [TAKEN — Castellan #1]</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>a Knight Castellan</t>
+          <t>Knight Castellan</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Castellan -&gt; T13: pushes S12-13 anti-tank (rail / ferrumite / lascannon / Caladius / thermal) from wounding on 4+ to 5+ — survivability for the key Volcano platform. The 2-Armiger build fits ~one enhancement; this is it.</t>
+          <t>Re-roll the number of Attacks (shots) of a weapon — huge on the Volcano lance (D3 shots) and plasma decimator (D6+3), turning low shot-rolls into full salvoes. The shooting-dominant enhancement.</t>
         </is>
       </c>
       <c r="E17" s="9" t="n"/>
@@ -822,54 +822,30 @@
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Bearer of the Judicant's Helm  [bench]</t>
+          <t>Blessed Plate  [TAKEN — Castellan #2]</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>a Knight Castellan</t>
+          <t>Knight Castellan</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>[Ignores Cover] on a Castellan — stacks with Dominus +1-hit-in-terrain. Offensive alternative to Blessed Plate.</t>
+          <t>Castellan -&gt; T13: pushes S12-13 anti-tank (rail / ferrumite / lascannon / Caladius / thermal) from wounding on 4+ to 5+ — survivability for the second Volcano platform.</t>
         </is>
       </c>
       <c r="E18" s="9" t="n"/>
     </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Sanctuary  [bench]</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>a Knight Castellan</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>5++ invuln vs MELEE on one Castellan — patches the no-melee-invuln weakness (newly relevant: 11E has NO Rotate Ion Shields and Questoris have no melee save). Consider vs a melee-heavy field.</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="D19:E19"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B3:E3"/>
@@ -2038,7 +2014,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>The durability lever: upgrade ONE Knight to 4++ vs shooting each turn. [VERIFY exact Valourstrike stratagem name/wording vs the LIVE faction pack — the 11E datasheet Ion Shield is the printed '5+* vs ranged only'; confirm the detachment grants the per-turn 4++.]</t>
+          <t>VALOURSTRIKE 1CP STRATAGEM: +1 to a Knight's invulnerable save vs SHOOTING (5++ -&gt; 4++) for the phase. The core durability lever in the hard shooting matchups — cycle it onto the focused Knight each turn. (Stratagems ARE the detachment: how Valourstrike actually plays.)</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2050,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>VERIFIED 72" D3 SHOTS (avg 2), S18 AP-5 D6+8 [Blast] — ~23 dmg/turn; one-shots no-invuln anchors (Hammerheads T10, Land Raiders T12, Kataphrons, Shadowsword, no-invuln Norns/Emissaries). Overkill into low-W chaff. The Castellan is 400pts (BSData; app may price 425 — verify vs live MFM).</t>
+          <t>VERIFIED 72" D3 SHOTS (avg 2), S18 AP-5 D6+8 [Blast] — ~23 dmg/turn; one-shots no-invuln anchors (Hammerheads T10, Land Raiders T12, Kataphrons, Shadowsword, no-invuln Norns/Emissaries). Overkill into low-W chaff. The Castellan is 425/450 pts (escalating: 1st 425, 2nd 450 — MFM).</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2149,7 @@
     <row r="2" ht="150" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Realistic 300+ GT expectation (re-verified): a positive-but-underdog record, roughly 3-3 to 4-2 over 5-6 rounds (~55-65% game win rate, pairing-skewed). Bank the broad early/mid field (the favourable + winnable coin-flips); slide toward losses as the top cut concentrates the filth (Necrons/T'au/Ravenwing/AdMech/SW). Correct Knight goal: strong positive + steal a couple you shouldn't win — NOT winning the event. The 2-Castellan shooting core IMPROVES this over 2-Lancer (more removal-race firepower for exactly the hard matchups). List blind spots (priority order): (1) [RESOLVED] now costed to 1,995/2000 (2nd Armiger + Blessed Plate); (2) only ONE 4++ Lancer into a melee-heavy field — accepted price of shooting-dominance; mitigate by killing deliverers pre-charge, NOT a 2nd blade; (3) screening deep-strike alphas (BA/SW/Votann/GSC) with only ~5 combat models — the Navigator dome is load-bearing; (4) anti-horde is moderate (accept Green Tide); (5) out-OC'd by most of the field -&gt; lock PURGE THE FOE (kill-weighted) over Priority Assets.</t>
+          <t>Realistic 300+ GT expectation (re-verified): a positive-but-underdog record, roughly 3-3 to 4-2 over 5-6 rounds (~55-65% game win rate, pairing-skewed). Bank the broad early/mid field (the favourable + winnable coin-flips); slide toward losses as the top cut concentrates the filth (Necrons/T'au/Ravenwing/AdMech/SW). Correct Knight goal: strong positive + steal a couple you shouldn't win — NOT winning the event. The 2-Castellan shooting core IMPROVES this over 2-Lancer (more removal-race firepower for exactly the hard matchups). List blind spots (priority order): (1) [RESOLVED] costed to 1,970/2000 (1 Armiger + Archeotech Autoloaders + Blessed Plate); (2) only ONE 4++ Lancer into a melee-heavy field — accepted price of shooting-dominance; mitigate by killing deliverers pre-charge, NOT a 2nd blade; (3) screening deep-strike alphas (BA/SW/Votann/GSC) with only ~5 combat models — the Navigator dome is load-bearing; (4) anti-horde is moderate (accept Green Tide); (5) out-OC'd by most of the field -&gt; lock PURGE THE FOE (kill-weighted) over Priority Assets.</t>
         </is>
       </c>
     </row>

--- a/docs/Reports & Plans/LSO-Knights-List-and-Analysis.xlsx
+++ b/docs/Reports & Plans/LSO-Knights-List-and-Analysis.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Backfield 48" autocannon platform + OC6 screen.</t>
+          <t>Backfield 48" autocannon platform — BOND TO THE CRUSADER (Crusader's Duty Bondsman = +1 to hit -&gt; BS2+, 8 shots): consistent anti-infantry/light removal that fills the list's anti-scorer gap. Survivable OC6 home/backfield anchor (you're out-OC'd by most of the field) + Suppression Protocols (-1 to hit its target). Chosen over a Warglaive: the list's anti-tank is already over-solved (2x Volcano + thermal + shieldbreaker + Lancer), so add ranged volume + a body that survives to score, not a fragile forward melee piece that duplicates the Lancer.</t>
         </is>
       </c>
     </row>

--- a/docs/Reports & Plans/LSO-Knights-List-and-Analysis.xlsx
+++ b/docs/Reports & Plans/LSO-Knights-List-and-Analysis.xlsx
@@ -1968,7 +1968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2102,15 +2102,27 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="19" t="inlineStr">
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Helverin Bondsman (EVERY TURN)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Keep the Armiger Helverin within Bondsman range of the KNIGHT CRUSADER -&gt; Crusader's Duty = +1 to hit = BS2+ on its 8 autocannon shots (48"). It is your SAFE backfield/home OC6 anchor + Suppression (-1 to hit its target) -- do NOT push it forward, and don't let it drift out of the Crusader's bond.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>MINDSET</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Knights are 'always outnumbered, rarely outgunned.' At a 300+ GT, START every hard matchup from the EXPECTATION OF A LOSS and hunt the HEIST. Model the opponent playing OPTIMALLY. Realistic goal: a strong POSITIVE record + steal a couple you shouldn't win — not winning the event. The 2 Volcano lances win the shooting phase; the Lancer wins the melee phase you can't tank; you win the game on the mission (out-OC where you can).</t>
         </is>
@@ -2118,9 +2130,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Reports & Plans/LSO-Knights-List-and-Analysis.xlsx
+++ b/docs/Reports & Plans/LSO-Knights-List-and-Analysis.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>The one blade: 4++ FULL invuln vs ALL, M14 W28. Counter-charge + assassinate buff-characters + Shock-Charge free Tank Shock on the charge.</t>
+          <t>The one blade: 4++ FULL invuln vs ALL, M14 W28. Counter-charge + kill characters (standalone monsters/Titanic DIRECTLY; ATTACHED buff-characters via EPIC CHALLENGE — 1CP core strat granting its melee [PRECISION]) + Shock-Charge free Tank Shock.</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
         <is>
           <t>• Deny the alpha, don't fight it: layered chaff/bubble-wrap so DC land 9"+ out, eat overwatch, can't reach T2. Castle T1-2.
 • Avenger gatling OVERWATCH the drop (A18 S6 AP-2 into 2W-T4 DC) thins it before it swings.
-• Lancer = counter-charge assassin: blank the multipliers — Lemartes (-1 Dmg), Sanguinary Priests (FNP5+/+1AP), Chaplains (strip Black Rage -&gt; DC go OC0, can't Fall Back).
+• Lancer + EPIC CHALLENGE (1CP): charge the DC/Sang-Guard unit and Precision-kill the ATTACHED multiplier — Lemartes (-1 Dmg) / Sanguinary Priest (FNP5+/+1AP) / Chaplain. You CANNOT snipe them at range; alternatively clear the small unit to expose them.
 • Win on the MISSION: out-OC massively (OC10/6 vs OC1 infantry). Do NOT try to table them.</t>
         </is>
       </c>
@@ -1968,7 +1968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>VERIFIED 415pts, M14 T11 W28, 4++ invuln vs ALL attacks (no asterisk). Shock lance STRIKE 5A WS2+ S20 AP-3 D8 [Lance] (wounds anything &lt;=T12 on 2s) / SWEEP 10A S10 AP-2 D3. Shock Charge = free Tank Shock (0CP, repeatable) on the charge = bonus MW. The universal counter-charge + character-assassin.</t>
+          <t>VERIFIED 415pts, M14 T11 W28, 4++ invuln vs ALL attacks (no asterisk). Shock lance STRIKE 5A WS2+ S20 AP-3 D8 [Lance] (wounds anything &lt;=T12 on 2s) / SWEEP 10A S10 AP-2 D3. Shock Charge = free Tank Shock (0CP) on the charge. Character-assassin: standalone monster/Titanic characters DIRECTLY; ATTACHED characters via EPIC CHALLENGE (1CP core strat -&gt; [PRECISION] in melee). No Knight GUN has Precision -&gt; you canNOT snipe attached characters at range.</t>
         </is>
       </c>
     </row>
@@ -2114,15 +2114,51 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>Killing characters (NO Precision on any Knight)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>You CANNOT target a Character attached to a Bodyguard unit — every wound goes to the bodyguard (no Knight GUN has [PRECISION], so you canNOT snipe at range). Tools: (1) EPIC CHALLENGE (core strat 15.03, 1CP): in the FIGHT phase a Knight CHARACTER's melee weapons gain [PRECISION] -&gt; the Lancer (5x S20 AP-3 D8) charges the unit and deletes the attached character. (2) STANDALONE Monster/Vehicle/Titanic characters (Fulgrim, Magnus, Lion, Daemon Princes, Steel-Hammer superheavies, enemy Knights) = shoot/fight DIRECTLY, no strat. (3) Clear a SMALL bodyguard whole to expose the character. (4) Lone Operatives = only targetable within 12".</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>CP economy (verify against list-building)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>~2 CP/round (1 at the start of EACH player-turn), ~10/game; + rare discard-a-secondary (max +1/turn) + CP-granting models. Each Strat is once/phase and costs CP. Rotate Ion Shields (1CP) and Epic Challenge (1CP) COMPETE each turn — plan the spend. HONOURED (Code Chivalric Deed completed) = +2 CP (3 if you rolled the Oath), exempt from the per-round cap -&gt; a real CP engine; completing a Deed EARLY funds Rotate + Epic Challenge all game.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Code Chivalric (the Oath — pick per matchup)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1 Deed + 1 Quality at deploy. QUALITY (army-wide, all game): MARTIAL VALOUR (re-roll 1 hit + 1 wound shoot/fight = the shooting amplifier, DEFAULT) / LEGACY (+2 OC, +1 Ld = the out-OC fix vs hordes) / EAGER (+2" M, +1 Adv &amp; Charge = land the Lancer + out-manoeuvre). DEED (complete once -&gt; Honoured +2/3CP): REAP A TALLY (destroy &gt; round-number units this round — fast for a gun list) / LAY LOW THE TYRANT (kill a named enemy CHARACTER — only vs a STANDALONE/Titanic linchpin you can actually kill, or an attached one the Lancer can Epic-Challenge) / RECLAIM THE REALM (out-OC them — AVOID, you're usually out-OC'd). See CODE_CHIVALRIC for the per-archetype picks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>MINDSET</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Knights are 'always outnumbered, rarely outgunned.' At a 300+ GT, START every hard matchup from the EXPECTATION OF A LOSS and hunt the HEIST. Model the opponent playing OPTIMALLY. Realistic goal: a strong POSITIVE record + steal a couple you shouldn't win — not winning the event. The 2 Volcano lances win the shooting phase; the Lancer wins the melee phase you can't tank; you win the game on the mission (out-OC where you can).</t>
         </is>
@@ -2130,9 +2166,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A17:B17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Reports & Plans/LSO-Knights-List-and-Analysis.xlsx
+++ b/docs/Reports & Plans/LSO-Knights-List-and-Analysis.xlsx
@@ -1968,7 +1968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2150,15 +2150,27 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>Battle-shock — the wounded-Knight trap</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Core 01.07 + the rulebook's own VEHICLE example: a single-model unit BELOW HALF its Wounds must take a battle-shock roll (Ld) every Command phase. A damaged Castellan (&lt;12 of 24W), Crusader (&lt;11 of 22), Lancer (&lt;14 of 28) or Helverin (&lt;6 of 12) therefore rolls each turn, and on a FAIL it (a) has OC '-' (0) so it stops holding objectives, (b) CANNOT be targeted by stratagems -&gt; you canNOT Rotate Ion Shields it the very turn it's hurt and most needs the 4++, and (c) can't do Actions. So a hurt Knight can be locked out of its own durability lever. Mitigate: LEGACY UNSULLIED Quality (+1 Ld eases the roll) and INSANE BRAVERY (core 15.04, 1CP: auto-pass ONE test — save it for the Knight you MUST Rotate next turn). WEAPONIZED at LSO by Tyranids (Shadow in the Warp forces ALL your units to test, on 3D6 near synapse), Necrons (1CP C'tan strat, forced test at -1 + D3+1 mortals), CSM and Chaos Daemons (Fear/forced tests). Vs those decks, keep a Knight either above half or above-half-and-screened, and bank a CP for Insane Bravery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>MINDSET</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="90" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Knights are 'always outnumbered, rarely outgunned.' At a 300+ GT, START every hard matchup from the EXPECTATION OF A LOSS and hunt the HEIST. Model the opponent playing OPTIMALLY. Realistic goal: a strong POSITIVE record + steal a couple you shouldn't win — not winning the event. The 2 Volcano lances win the shooting phase; the Lancer wins the melee phase you can't tank; you win the game on the mission (out-OC where you can).</t>
         </is>
@@ -2167,8 +2179,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A17:B17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Reports & Plans/LSO-Knights-List-and-Analysis.xlsx
+++ b/docs/Reports & Plans/LSO-Knights-List-and-Analysis.xlsx
@@ -1937,7 +1937,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Unsaveable Sternguard Dev (full wound-reroll vs Oath) + sticky OC10 Intercessors + un-shockable OC22 Lysander Terminator brick + Armour of Contempt + a ~30-34 Oath-convergence alpha. Sisters 98-31 lesson: durable + sticky + volume.</t>
+          <t>Unsaveable Sternguard Dev (full wound-reroll vs Oath) + sticky OC10 Intercessors + an OC22 Lysander Terminator brick (NOT battle-shock-immune, but Knights have no way to force a test) + Armour of Contempt + a ~30-34 Oath-convergence alpha. Sisters 98-31 lesson: durable + sticky + volume.</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
